--- a/data/deelnemers.xlsx
+++ b/data/deelnemers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dairyconsultnl-my.sharepoint.com/personal/albart_dairyconsult_nl/Documents/Documenten/online_dingen/studiereis_italie/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{3E5DC795-0A24-49F3-AF6B-AC42BF4E79D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EBCB307-47D5-4FDB-823F-AB163DA82A25}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{3E5DC795-0A24-49F3-AF6B-AC42BF4E79D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{979CD0A3-FC16-4AFB-B9A6-2C9378558C67}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF6969EC-B037-4E7D-8F0A-773924E089C1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="95">
   <si>
     <t>Koen</t>
   </si>
@@ -300,6 +300,30 @@
   </si>
   <si>
     <t>gbrplatkow@t-online.de</t>
+  </si>
+  <si>
+    <t>Leo</t>
+  </si>
+  <si>
+    <t>Kool</t>
+  </si>
+  <si>
+    <t>info@kaasboerderijkool.nl</t>
+  </si>
+  <si>
+    <t>06 10801266</t>
+  </si>
+  <si>
+    <t>Anton</t>
+  </si>
+  <si>
+    <t>Klein Swormink</t>
+  </si>
+  <si>
+    <t>Mtskleinswormink@outlook.com</t>
+  </si>
+  <si>
+    <t>31 6 42736541</t>
   </si>
 </sst>
 </file>
@@ -719,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7BC42E-44F1-4D18-B09F-A39973ECADE8}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -1074,6 +1098,34 @@
       </c>
       <c r="D25" s="5" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1092,8 +1144,9 @@
     <hyperlink ref="C20" r:id="rId12" display="mailto:jj_dijkstra@yahoo.com" xr:uid="{34647225-865E-4F2D-B1EF-38936054C36A}"/>
     <hyperlink ref="C17" r:id="rId13" display="mailto:gbrplatkow@t-online.de" xr:uid="{F0C1DB9B-E87F-40B6-B5E2-4D138AA05C36}"/>
     <hyperlink ref="C18" r:id="rId14" display="mailto:gbrplatkow@t-online.de" xr:uid="{CA276E73-2717-4C7B-97F0-CBD544B348AF}"/>
+    <hyperlink ref="C26" r:id="rId15" xr:uid="{BC9950A6-9DEE-4F0D-A09E-E91338F14FCB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
--- a/data/deelnemers.xlsx
+++ b/data/deelnemers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dairyconsultnl-my.sharepoint.com/personal/albart_dairyconsult_nl/Documents/Documenten/online_dingen/studiereis_italie/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{3E5DC795-0A24-49F3-AF6B-AC42BF4E79D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{979CD0A3-FC16-4AFB-B9A6-2C9378558C67}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{1A1FFF6B-DDDD-4958-A45B-D6051B2EEE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76F6262B-5904-440A-8F86-628943672696}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BF6969EC-B037-4E7D-8F0A-773924E089C1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="98">
   <si>
     <t>Koen</t>
   </si>
@@ -47,9 +47,6 @@
     <t>van Leeuwen</t>
   </si>
   <si>
-    <t>koen@vrolijkekoe.nl</t>
-  </si>
-  <si>
     <t>Josine</t>
   </si>
   <si>
@@ -122,15 +119,6 @@
     <t>Willie</t>
   </si>
   <si>
-    <t>Jan Jetzes</t>
-  </si>
-  <si>
-    <t>Bakker</t>
-  </si>
-  <si>
-    <t>Jetze</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jan </t>
   </si>
   <si>
@@ -209,12 +197,6 @@
     <t>alandman@freenet.de</t>
   </si>
   <si>
-    <t>jetzebakker2002@gmail.com</t>
-  </si>
-  <si>
-    <t>janjetzes@gmail.com</t>
-  </si>
-  <si>
     <t>Martin</t>
   </si>
   <si>
@@ -266,12 +248,6 @@
     <t>+49 175 2941401</t>
   </si>
   <si>
-    <t>+31 6 10291858</t>
-  </si>
-  <si>
-    <t>+31 6 51088664</t>
-  </si>
-  <si>
     <t>+49 171 3735381</t>
   </si>
   <si>
@@ -324,6 +300,39 @@
   </si>
   <si>
     <t>31 6 42736541</t>
+  </si>
+  <si>
+    <t>naam</t>
+  </si>
+  <si>
+    <t>achternaam</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>telefoon</t>
+  </si>
+  <si>
+    <t>Jacob Jan</t>
+  </si>
+  <si>
+    <t>Tuinier Hofman</t>
+  </si>
+  <si>
+    <t>jan.tuinierhofman@stoverland.de</t>
+  </si>
+  <si>
+    <t>00491723816689</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>00491728723715</t>
+  </si>
+  <si>
+    <t>linda.tuinierhofman@stoverland.de</t>
   </si>
 </sst>
 </file>
@@ -743,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC7BC42E-44F1-4D18-B09F-A39973ECADE8}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
@@ -752,366 +761,366 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>69</v>
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>60</v>
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>61</v>
+        <v>51</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>75</v>
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="4">
+        <v>31613680011</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D14" s="4">
-        <v>31613680011</v>
+        <v>31648052901</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="4">
-        <v>31648052901</v>
+        <v>30</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>77</v>
+        <v>32</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>85</v>
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>37</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>80</v>
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="6">
+        <v>31653406874</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>42</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C23" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="6">
-        <v>31653406874</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>73</v>
+        <v>53</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" t="s">
-        <v>90</v>
+        <v>84</v>
+      </c>
+      <c r="C26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1121,32 +1130,47 @@
       <c r="B27" t="s">
         <v>92</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>94</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1" xr:uid="{D0BCCEC4-9C0B-4216-94F2-6787594AC399}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{3DF9B7D3-BD0E-4E04-8E07-D7F27292245B}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{542B2A25-6842-4497-8D10-913B5644ABE3}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{D5D77B57-F3A0-4659-9446-17C6BDAA6FE3}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{7A9FCD3D-F719-4D66-AA45-9D9E2EB862DD}"/>
-    <hyperlink ref="C19" r:id="rId6" display="mailto:v.westeinde@outlook.com" xr:uid="{E8FEB684-EB94-4AAC-B118-389C4C779C57}"/>
-    <hyperlink ref="C25" r:id="rId7" display="mailto:Mtsimmink@hotmail.com" xr:uid="{A3E1A4A8-245A-4CE1-A4C3-B361731BE7BE}"/>
-    <hyperlink ref="C15" r:id="rId8" display="mailto:Melkveebedrijf@haskerweide.nl" xr:uid="{A7F12619-52A7-48E0-A8ED-A6D230971AEA}"/>
-    <hyperlink ref="C14" r:id="rId9" display="mailto:Melkveebedrijf@haskerweide.nl" xr:uid="{5B65DED9-9016-4BE5-8778-D531F18B3B72}"/>
-    <hyperlink ref="C9" r:id="rId10" display="mailto:k.zijlstra@tzg-heinersdorf.de" xr:uid="{269A084F-FD7F-41F3-9751-0E1D735A5D1F}"/>
-    <hyperlink ref="C21" r:id="rId11" display="mailto:sjefenwilma@hotmail.com" xr:uid="{94E2BDBA-F1B0-4DE7-A73C-CDB51EA02311}"/>
-    <hyperlink ref="C20" r:id="rId12" display="mailto:jj_dijkstra@yahoo.com" xr:uid="{34647225-865E-4F2D-B1EF-38936054C36A}"/>
-    <hyperlink ref="C17" r:id="rId13" display="mailto:gbrplatkow@t-online.de" xr:uid="{F0C1DB9B-E87F-40B6-B5E2-4D138AA05C36}"/>
-    <hyperlink ref="C18" r:id="rId14" display="mailto:gbrplatkow@t-online.de" xr:uid="{CA276E73-2717-4C7B-97F0-CBD544B348AF}"/>
-    <hyperlink ref="C26" r:id="rId15" xr:uid="{BC9950A6-9DEE-4F0D-A09E-E91338F14FCB}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{3DF9B7D3-BD0E-4E04-8E07-D7F27292245B}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{542B2A25-6842-4497-8D10-913B5644ABE3}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{D5D77B57-F3A0-4659-9446-17C6BDAA6FE3}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{7A9FCD3D-F719-4D66-AA45-9D9E2EB862DD}"/>
+    <hyperlink ref="C18" r:id="rId5" display="mailto:v.westeinde@outlook.com" xr:uid="{E8FEB684-EB94-4AAC-B118-389C4C779C57}"/>
+    <hyperlink ref="C24" r:id="rId6" display="mailto:Mtsimmink@hotmail.com" xr:uid="{A3E1A4A8-245A-4CE1-A4C3-B361731BE7BE}"/>
+    <hyperlink ref="C14" r:id="rId7" display="mailto:Melkveebedrijf@haskerweide.nl" xr:uid="{A7F12619-52A7-48E0-A8ED-A6D230971AEA}"/>
+    <hyperlink ref="C13" r:id="rId8" display="mailto:Melkveebedrijf@haskerweide.nl" xr:uid="{5B65DED9-9016-4BE5-8778-D531F18B3B72}"/>
+    <hyperlink ref="C10" r:id="rId9" display="mailto:k.zijlstra@tzg-heinersdorf.de" xr:uid="{269A084F-FD7F-41F3-9751-0E1D735A5D1F}"/>
+    <hyperlink ref="C20" r:id="rId10" display="mailto:sjefenwilma@hotmail.com" xr:uid="{94E2BDBA-F1B0-4DE7-A73C-CDB51EA02311}"/>
+    <hyperlink ref="C19" r:id="rId11" display="mailto:jj_dijkstra@yahoo.com" xr:uid="{34647225-865E-4F2D-B1EF-38936054C36A}"/>
+    <hyperlink ref="C16" r:id="rId12" display="mailto:gbrplatkow@t-online.de" xr:uid="{F0C1DB9B-E87F-40B6-B5E2-4D138AA05C36}"/>
+    <hyperlink ref="C17" r:id="rId13" display="mailto:gbrplatkow@t-online.de" xr:uid="{CA276E73-2717-4C7B-97F0-CBD544B348AF}"/>
+    <hyperlink ref="C25" r:id="rId14" xr:uid="{BC9950A6-9DEE-4F0D-A09E-E91338F14FCB}"/>
+    <hyperlink ref="C27" r:id="rId15" display="mailto:jan.tuinierhofman@stoverland.de" xr:uid="{B3EC27A8-69F2-4019-BA63-CA9E76108FBA}"/>
+    <hyperlink ref="C28" r:id="rId16" xr:uid="{0DEEA8D8-3CF7-46B9-B686-329C8BD9EB0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId16"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId17"/>
 </worksheet>
 </file>